--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46274</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>46265</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45399</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>45080</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46274</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45744</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45945</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45947</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45744</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>44516</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>46101</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>46274</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>46210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46197</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44959</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45897</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>46213</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>46197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>46266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45012</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45869</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>46205</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>46251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>46078</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>46243</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45744</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45792</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>45623</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>46126</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45694</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45694</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45199</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>45694</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45175</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>46220</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>46220</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>46266</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>46265</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>46251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>46244</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45892</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45213</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45062</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45709</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>46092</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>46136</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45834</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>44942</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45862</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>46210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>46220</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>45190</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>46282</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>46282</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46113</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>44960</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44953</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45688</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45420</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>46099</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44575</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44684</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44607</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44886</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>44862</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44854</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>44550</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>44799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44854</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44697</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44672</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44616</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44823</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44781</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44788</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>44473</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44607</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44783</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45033</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45212</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>45413</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44832</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>45413</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45413</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44854</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45469</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>44904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45796</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>45110</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45796</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45474</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44953</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>46021</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45463</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45150</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45154</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>46030</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>46029</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>44886</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45798</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45797</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>46030</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>46030</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>46030</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45797</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>46031</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>46034</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45688</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45240</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45888</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45887</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>46035</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45889</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45889</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>46038</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>46034</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>45889</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45898</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>45902</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45902</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45902</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45902</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45908</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45905</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45908</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45201</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>45198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45280</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>46057</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>46065</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46065</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>46065</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>45561</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45804</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45751</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>45925</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45925</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45833</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45930</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>46080</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45805</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45805</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45805</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>45810</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45936</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44953</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46091</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45936</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45615</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>46091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44960</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45212</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45548</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45939</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45943</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45943</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45237</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45874</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>44494</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>46101</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45946</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45096</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45117</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45148</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45552</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45552</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45244</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45874</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45946</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45467</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>46100</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45950</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>45600</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45950</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45950</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>46104</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45112</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45952</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45952</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45952</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45954</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45463</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45954</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45955</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45957</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45957</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46114</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45960</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>46119</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>46122</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45972</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46126</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45400</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45727</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45980</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46134</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45980</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45980</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>46134</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>46133</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45985</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45708</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45615</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44750</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45154</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45063</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45414</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45201</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>44482</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45999</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>45999</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45999</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45999</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>45999</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>46002</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45150</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>46001</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45051</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>45819</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45190</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46003</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45743</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46008</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45839</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>46008</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45773</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>46013</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44895</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45824</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46140</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45196</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45742</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45639</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45827</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45176</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45834</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45027</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>46141</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44965</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>46149</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45832</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45834</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45237</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45237</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45960</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45238</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45229</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45259</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45834</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45834</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45833</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45588</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>45833</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45892</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45960</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>45561</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45463</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>45840</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45841</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45182</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44916</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45845</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45843</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>46163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45845</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>46163</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>44550</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45855</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45561</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>46169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45855</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45855</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>46175</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>46175</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45601</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45870</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45870</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45870</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45870</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45870</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>46181</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>44937</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45874</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45265</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>46184</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45481</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>46185</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44986</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>46185</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45798</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45873</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>46190</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>46191</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>46192</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>46192</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45665</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>46195</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>46197</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46197</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>46197</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45880</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>45882</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45573</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45881</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>46199</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>46199</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>46198</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>46198</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45882</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>45579</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>46204</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>46204</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>46205</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>46205</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>46205</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>46205</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45196</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45196</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>46204</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>46204</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>46204</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>46205</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>46204</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>46120</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>46252</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>46251</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>46252</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>46206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>46206</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45199</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44609</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46210</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46254</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46254</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>46254</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>46254</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>46254</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>46255</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>46258</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>46255</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45147</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45146</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45561</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>45561</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>46216</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>46217</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>46177</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>46216</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45279</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44726</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>45196</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>46266</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45201</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>46266</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>46266</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>46266</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>46266</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>46266</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>46265</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>46265</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45727</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>46225</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>46225</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45190</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>46266</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>46267</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>46225</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>46225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>46269</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>46267</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>46267</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45309</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>46267</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>45723</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36913,7 +36913,7 @@
         <v>46269</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>45264</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>46267</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>46269</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45482</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>46231</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44904</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46273</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>46231</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45219</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>46274</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>46273</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46273</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46273</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>46231</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>46274</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>46275</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45362</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46275</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>46274</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>46275</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>46275</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>46279</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>46279</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46274</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>46274</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>46279</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>45665</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>46279</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45362</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>46237</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>46281</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>46273</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>46281</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>46280</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>46286</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>46243</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>46244</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45870</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>46286</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>46204</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>44505</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45898</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46287</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45337</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45337</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>44875</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46244</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>44588</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44624</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>44942</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44942</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>46248</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45561</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>45908</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>46286</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>46289</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45604</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>44607</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45190</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45616</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45196</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45212</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45637</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45679</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45033</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45077</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>45121</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45188</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45377</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45463</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44953</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45272</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45215</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45705</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>45454</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45792</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45792</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>44612</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>44960</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45027</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44943</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45756</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45769</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46065</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45777</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>45777</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>

--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>46265</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45744</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45399</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45945</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45947</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45744</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44516</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46101</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46197</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>44959</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45897</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>46213</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>46197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>46266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45744</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45869</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>46205</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>45012</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>46078</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45469</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46243</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>46251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45199</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>45623</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>45694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>46126</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45694</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45694</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46213</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>46220</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>46265</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>46220</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45175</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>46266</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>46266</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>46244</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>46251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45476</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44960</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45892</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45709</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>45894</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45213</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>46092</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45834</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45751</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45062</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>45190</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45420</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>46136</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45862</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>45688</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>46210</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>46220</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>46265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>46282</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>46282</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>46113</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>46293</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>44953</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44942</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>46099</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44575</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44684</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44886</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44862</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44854</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44607</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44799</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44854</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44697</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44616</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>44616</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>44823</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44781</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>44788</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44473</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44607</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45146</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44875</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45077</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45309</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45212</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45454</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45272</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45265</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45154</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45337</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>46003</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>46002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>46008</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45665</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>46008</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>46013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>46013</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45110</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45889</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45889</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>46021</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45889</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45889</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45413</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>46030</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>46030</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>45898</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46030</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>46030</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>46031</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>46035</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>46034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>46034</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45688</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45902</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>46034</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45902</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45905</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>46038</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45908</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45237</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45908</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45792</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45796</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45797</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45797</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45798</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45805</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45805</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45804</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45805</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45925</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45925</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>46057</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45930</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>46065</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45413</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>46065</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45238</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45615</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45936</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45936</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>46065</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>44588</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45943</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45939</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45190</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44494</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45874</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45096</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45148</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45244</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45117</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45552</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45552</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45874</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45467</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45467</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>46076</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45946</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45946</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45219</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>45033</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45946</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44832</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45950</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45950</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45833</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>45950</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>46080</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45215</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45952</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45952</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45952</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45150</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45196</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45954</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45196</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45957</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45957</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45955</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45954</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45063</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>46091</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45960</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>46091</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45604</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45463</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44726</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>45400</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>44607</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45196</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45196</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46100</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45482</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45972</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>46101</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>46104</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45548</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45819</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45980</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45414</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>45980</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45980</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45985</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>45469</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>44895</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>46114</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45986</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>46119</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45463</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45474</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>46122</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45827</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>46126</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>45999</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45999</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45999</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>46127</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45999</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45999</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45579</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46133</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45201</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45832</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45833</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>46134</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45833</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>46134</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45834</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45834</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45834</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45834</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45561</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45561</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45121</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45229</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45840</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45212</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45841</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45845</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45843</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45845</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44505</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45665</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45855</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45855</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>45855</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46141</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45639</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45834</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>46140</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45705</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>45150</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44937</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45870</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45870</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44854</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45839</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45870</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45873</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45198</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>45798</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45870</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>46149</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45743</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45870</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45708</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45874</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45892</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>45960</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>46163</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44750</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>46162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>46163</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>44942</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45033</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45880</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>46169</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>44896</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45637</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45882</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45882</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45588</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>46175</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45881</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>46175</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45887</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45573</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45199</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>46181</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>46184</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44911</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45212</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>46185</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46185</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>46190</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>44953</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>46192</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>46192</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>46195</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44783</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>46197</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>45237</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>46198</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>46197</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46198</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45615</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>46197</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46199</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>46199</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>46204</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>46204</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>46204</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>46204</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>46204</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>46204</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>46206</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45601</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>46205</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46120</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>46205</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44904</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
         <v>46205</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>46205</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>46205</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>46206</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45463</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>44942</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45147</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>46210</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>46216</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>46216</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45259</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>46258</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45337</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>46177</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45481</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>46265</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>46265</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>46266</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>46266</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>46266</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>46267</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45561</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>46266</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46266</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46266</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>46266</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>44609</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>46267</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>46225</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>46267</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45154</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>46225</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46225</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>46225</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44992</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>46267</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>46273</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>46273</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45723</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>46269</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>46269</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>46273</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>46267</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>46231</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>46274</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>46273</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>46275</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46275</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>46274</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>46275</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46231</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46231</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>46274</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>46275</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45362</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>46279</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>46279</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>46279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>46279</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>46237</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46274</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>46281</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46281</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>46280</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45027</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45600</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>46274</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46273</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45362</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45264</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45463</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44818</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>46286</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46286</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>46244</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45870</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39552,7 +39552,7 @@
         <v>45898</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46243</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>44986</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>46287</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>46248</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>46293</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>46289</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45201</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>46293</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45908</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>46293</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>46293</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>46204</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>44886</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>46293</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>46265</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>46286</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>46251</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45051</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>46294</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>46252</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>46252</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45413</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>46255</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46296</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>46217</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44953</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>46244</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>44904</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>46254</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>46254</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>46255</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>46254</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>46254</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>46254</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>46254</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>45377</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>45561</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>44550</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>44624</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>45190</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45237</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45279</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45773</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45280</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45112</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45561</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45561</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>45616</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>44916</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>45727</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45201</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>44960</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45027</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>44612</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>44943</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45756</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45769</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>46065</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45777</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45777</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>

--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45945</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44739</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>46265</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45399</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45744</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44516</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46101</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46197</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45175</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>44959</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45897</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>46213</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>46197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>46266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45744</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45154</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45792</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>45869</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45469</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>46205</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>46243</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>45623</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45175</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45694</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45694</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45199</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>46213</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>46266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>46220</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>46220</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46266</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46265</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>46251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>46244</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>46301</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44942</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45688</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45892</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45420</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45751</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45062</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45894</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45834</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45190</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45862</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44960</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44953</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46136</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45213</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46092</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>46210</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>46220</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>46265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>46282</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>46282</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>46113</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46293</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>46301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46303</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>46099</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44575</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44684</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44862</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44854</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>44781</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44550</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44607</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44799</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44616</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44616</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44823</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44788</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44697</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>45637</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44832</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45413</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>45413</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45238</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45229</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45413</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45259</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44783</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45212</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45033</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45561</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45679</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44854</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45033</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45463</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45077</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45469</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45377</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44550</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45561</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45463</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45110</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44904</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45474</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44953</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44953</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45463</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45150</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45888</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45887</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45887</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44886</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45272</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45215</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45889</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45898</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45902</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45601</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45705</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45454</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45908</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>45905</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45908</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44937</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>44992</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45265</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45201</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44911</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45481</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>44986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45561</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45925</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44818</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45925</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45792</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45925</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45930</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45796</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45796</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45573</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45798</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45797</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>44953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45579</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45797</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44960</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45212</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45548</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45936</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45936</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45196</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45196</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45805</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45805</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45810</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>45600</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45537</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45199</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>44609</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45112</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45939</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45943</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45943</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45467</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45874</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44494</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45946</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45096</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45117</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45148</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45552</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45552</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45244</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45874</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45894</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45946</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45463</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45467</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45400</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45950</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>45063</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45414</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45819</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45950</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45147</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45146</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44895</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45950</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45950</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45561</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45561</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45827</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45952</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45952</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45832</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45952</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45954</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45954</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45955</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45957</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45960</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45834</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45279</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45834</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45834</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45834</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45833</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45833</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45840</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>44726</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45196</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45841</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45708</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45615</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45201</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44750</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45845</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>45843</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45845</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45154</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45727</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45201</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>44482</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45855</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45855</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45190</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45855</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45150</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45309</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45727</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45870</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45870</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45870</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45870</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45723</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45190</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45264</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45874</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45743</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45482</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45980</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44904</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45798</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45980</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45873</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45219</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45980</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45773</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45880</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45882</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45196</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45881</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45882</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45742</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>46101</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45665</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45985</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46100</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45986</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>46104</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45176</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45027</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44965</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>46114</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>46119</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46122</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>46127</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45999</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45999</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45999</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45999</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45999</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>46002</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46126</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>46001</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>44505</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>46134</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45337</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45337</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46134</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44875</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46003</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46133</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>44588</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>44624</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44942</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>46008</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44942</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>46008</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45561</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>46013</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>46013</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46021</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45604</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46030</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46029</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46030</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46030</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>46030</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>46034</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46031</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45688</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45240</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>46034</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44607</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45839</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45190</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45616</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>46035</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>46038</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46034</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45196</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>45212</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46140</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45639</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>46057</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45834</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46141</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>46065</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46065</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>46065</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>46149</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45960</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46076</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46080</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45892</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45960</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46091</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>46091</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45182</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>46163</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>46169</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46175</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46175</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46181</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>46184</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>46185</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46185</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>46190</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>46191</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>46192</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>46192</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>46195</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>46197</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>46197</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>46197</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46199</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46199</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>46198</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>46204</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>46204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>46205</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46205</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46205</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46205</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46204</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>46205</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>46204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46120</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>46206</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>46206</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46210</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46216</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>46177</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>46216</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>46266</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>46266</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>46266</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46266</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>46266</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>46266</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>46265</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46265</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>46225</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>46225</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>46266</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>46225</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>46225</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46269</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>46267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>46267</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46267</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>46269</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>46267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>46269</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>46231</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>46273</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>46231</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>46274</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>46273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>46273</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46273</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>46231</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>46274</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46275</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>46267</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45362</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>46275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>46274</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>46275</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>46279</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>46279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>46274</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>46279</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>46279</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45362</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>46237</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>46281</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>46273</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46281</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>46280</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46286</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46243</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46244</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45870</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46286</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45898</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46287</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45908</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>46294</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46293</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>46252</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>46293</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>46293</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>46252</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>46293</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>46204</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>46248</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46296</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>46265</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>46251</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>45051</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>46254</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46254</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>46254</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46254</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>46300</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>46217</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>46254</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>46254</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>46244</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46300</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46300</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>46301</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>46300</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46258</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46293</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>46303</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>46267</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>44612</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>44960</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45027</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44943</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45756</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45769</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>46065</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45777</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45777</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>

--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45945</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44739</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>46265</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45399</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45744</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45945</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44516</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46101</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46197</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45175</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>44959</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45897</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>46213</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>46197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>46266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45744</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45154</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45792</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>45869</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45469</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>46205</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>46243</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>45623</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45694</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45175</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45694</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45694</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45199</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>46213</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>46266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>46220</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>46220</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46266</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46265</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>46251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>46244</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>46301</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44942</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45688</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45892</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45420</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45751</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45062</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45894</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45834</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45190</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45862</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44960</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44953</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46136</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45213</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46092</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>46210</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>46220</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>46265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>46282</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>46282</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>46113</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46293</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>46301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46303</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>46099</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44575</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44684</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44862</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44854</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>44781</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44550</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44607</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44799</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44616</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44616</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44823</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44788</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44697</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>45637</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44832</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45413</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>45413</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45238</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45229</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45413</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45259</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44783</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45212</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45033</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45561</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45679</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44854</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45033</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45463</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45077</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45469</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45377</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44550</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45561</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45463</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45110</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44904</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45474</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44953</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44953</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45463</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45150</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45888</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45887</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45887</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44886</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45272</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45215</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45889</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45898</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45902</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45601</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45705</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45454</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45908</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>45905</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45908</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44937</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>44992</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45265</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45201</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44911</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45481</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>44986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45561</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45925</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44818</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45925</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45792</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45925</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45930</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45796</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45796</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45573</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45798</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45797</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>44953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45579</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45797</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44960</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45212</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45548</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45936</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45936</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45196</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45196</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45805</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45805</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45810</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>45600</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45537</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45199</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>44609</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45112</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45939</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45943</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45943</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45467</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45874</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44494</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45946</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45096</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45117</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45148</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45552</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45552</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45244</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45874</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45894</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45946</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45463</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45467</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45400</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45950</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>45063</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45414</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45819</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45950</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45147</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45146</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44895</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45950</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45950</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45561</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45561</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45827</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45952</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45952</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45832</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45952</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45954</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45954</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45955</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45957</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45960</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45834</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45279</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45834</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45834</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45834</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45833</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45833</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45840</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>44726</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45196</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45841</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45708</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45615</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45201</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44750</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45845</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>45843</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45845</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45154</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45727</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45201</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>44482</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45855</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45855</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45190</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45855</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45150</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45309</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45727</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45870</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45870</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45870</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45870</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45723</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45190</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45264</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45874</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45743</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45482</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45980</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44904</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45798</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45980</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45873</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45219</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45980</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45773</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45880</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45882</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45196</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45881</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45882</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45742</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>46101</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45665</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45985</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46100</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45986</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>46104</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45176</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45027</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44965</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>46114</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>46119</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46122</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>46127</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45999</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45999</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45999</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45999</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45999</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>46002</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46126</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>46001</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>44505</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>46134</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45337</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45337</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46134</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44875</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46003</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46133</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>44588</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>44624</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44942</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>46008</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44942</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>46008</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45561</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>46013</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>46013</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46021</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45604</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46030</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46029</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46030</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46030</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>46030</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>46034</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46031</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45688</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45240</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>46034</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44607</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45839</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45190</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45616</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>46035</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>46038</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46034</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45196</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>45212</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46140</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45639</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>46057</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45834</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46141</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>46065</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46065</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>46065</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>46149</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45960</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46076</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46080</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45892</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45960</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46091</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>46091</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45182</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>46163</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>46169</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46175</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46175</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46181</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>46184</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>46185</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46185</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>46190</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>46191</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>46192</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>46192</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>46195</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>46197</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>46197</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>46197</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46199</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46199</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>46198</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>46204</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>46204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>46205</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46205</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46205</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46205</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46204</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>46205</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>46204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46120</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>46206</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>46206</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46210</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46216</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>46177</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>46216</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>46266</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>46266</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>46266</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46266</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>46266</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>46266</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>46265</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46265</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>46225</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>46225</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>46266</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>46225</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>46225</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46269</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>46267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>46267</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46267</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>46269</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>46267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>46269</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>46231</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>46273</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>46231</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>46274</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>46273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>46273</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46273</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>46231</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>46274</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46275</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>46267</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45362</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>46275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>46274</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>46275</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>46279</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>46279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>46274</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>46279</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>46279</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45362</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>46237</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>46281</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>46273</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46281</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>46280</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46286</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46243</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46244</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45870</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46286</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45898</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46287</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45908</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>46294</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46293</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>46252</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>46293</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>46293</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>46252</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>46293</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>46204</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>46248</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46296</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>46265</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>46251</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>45051</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>46254</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>46254</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>46254</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46254</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>46300</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>46217</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>46254</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>46254</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>46244</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46300</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46300</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>46301</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>46300</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46258</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46293</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>46303</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>46267</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>44612</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>44960</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45027</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44943</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45756</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45769</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>46065</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45777</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45777</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>

--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>46265</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45744</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45399</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45945</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45744</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44516</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46101</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46197</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45175</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45897</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46197</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>46213</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44959</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46197</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>46266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45744</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45980</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>45154</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>45012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>46205</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>46078</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>46251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45792</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46243</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45199</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45694</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45623</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45694</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45694</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45175</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>46126</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>46220</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>46220</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45476</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>46266</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46309</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>46251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>46244</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46301</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45892</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>46136</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45751</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45062</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45190</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45709</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45420</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45894</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45213</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46210</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>46220</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>46282</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>46282</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>46113</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46293</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44942</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>46303</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>46309</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>46265</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>46301</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45834</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45862</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>46099</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44575</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44684</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>44607</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44886</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44862</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44854</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>44550</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44607</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44799</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44854</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44697</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44672</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44616</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44616</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44823</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>44781</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44788</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45146</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44875</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45309</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45077</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45679</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45212</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45454</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45272</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45265</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>45337</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44953</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45665</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44965</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45413</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45237</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45742</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45176</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>45238</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45190</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45219</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45150</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45033</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44832</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45215</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45463</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44726</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45482</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45548</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45469</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45413</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45881</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45463</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45474</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45110</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45887</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45887</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45189</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45888</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45889</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45889</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45579</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45201</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45898</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>46141</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45639</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45834</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46140</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45902</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45902</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45902</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45561</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45561</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45905</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45839</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45908</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45908</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45121</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45229</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45212</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44505</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45925</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45925</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45665</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45925</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>46149</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45930</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45615</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45936</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45936</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45196</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45943</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45943</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45939</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45892</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44494</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45096</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45148</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45244</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45117</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45552</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45552</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45874</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45894</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45467</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45467</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45946</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45960</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45946</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45705</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45950</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45950</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45960</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45950</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45950</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45952</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45952</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45952</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45150</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45954</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45957</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45955</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45954</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44937</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45960</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45182</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44854</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45972</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45727</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>46162</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45743</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>46163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45980</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45980</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45980</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>45985</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45986</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44750</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45999</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45999</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45999</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44942</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46169</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45033</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>46003</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46002</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>46008</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44896</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45637</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46008</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45588</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46013</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45573</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46021</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45199</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46029</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44911</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45212</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46175</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46030</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>46030</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46031</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46175</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>46035</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45240</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>46034</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>46034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45688</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>46034</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46038</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>46034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>44953</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46181</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44783</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46057</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46184</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45237</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45615</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46065</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>46065</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>46065</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>46185</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>46185</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46076</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45833</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>46080</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44904</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45463</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>46190</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44942</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45147</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46091</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46091</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46192</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>46191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>46192</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>46100</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46101</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45337</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>46104</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>46195</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46197</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45481</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>46197</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>46114</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>46198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>46197</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46119</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46199</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>46199</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>46122</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45561</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>44609</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>46126</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45154</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44992</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>46127</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45723</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46204</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46133</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46204</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>46134</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46134</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46204</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46204</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46204</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>46205</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>46205</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45027</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45600</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46205</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45264</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46205</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46205</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46206</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45463</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44818</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46210</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46216</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>46216</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46177</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>44986</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46225</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46225</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46225</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>46225</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46273</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>46273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>46273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>46231</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>46274</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46273</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>46275</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>46275</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45201</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46274</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>46275</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>46231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>46231</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>46274</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>46275</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>45362</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>46279</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>44886</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>46279</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>46279</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>46279</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>46237</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>46274</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>45188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>46281</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>46281</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>46280</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45413</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>46274</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>46273</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>45362</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44953</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>44904</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>46286</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46286</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46244</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>45377</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45870</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45561</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>44550</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45898</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>46243</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>44624</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>46287</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45190</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45237</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45279</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>46248</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45773</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45280</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46293</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>46289</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45112</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>46293</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45908</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>46293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>46293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46204</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45561</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45561</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46286</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>46251</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45051</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46294</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45616</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>46252</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>46252</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44916</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>46296</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>46217</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45727</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>46254</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>46254</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>46254</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>46254</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>46254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46254</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45201</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>46255</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>46300</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>46300</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46301</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>46258</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>46300</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>46300</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>46255</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>46303</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46293</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45792</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45792</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45796</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45797</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45797</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45796</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46120</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45798</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>46266</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>46266</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>46267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>46265</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46309</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46266</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46266</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46267</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>46267</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46309</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45805</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46308</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45805</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>45804</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46265</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45805</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46265</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46266</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>46267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46266</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46267</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>46309</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46266</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45537</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45810</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>46311</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45063</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46269</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45400</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>46269</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46269</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45819</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45414</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>44895</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46310</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45824</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46309</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>46309</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>46267</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45827</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>46311</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>45832</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45833</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45833</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45834</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45834</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45834</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45834</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45840</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45841</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45845</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45843</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45845</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45855</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>45855</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45855</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45870</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>45870</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>45870</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45873</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45798</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45870</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45874</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>45880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45882</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>45882</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>44960</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45027</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44612</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>44943</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45756</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45769</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>46065</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45777</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45777</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>

--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>46265</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45744</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45399</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45945</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45744</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44516</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46101</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>46274</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46197</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45175</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45897</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46197</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>46213</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44959</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46197</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>46266</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45744</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45980</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>45154</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>45012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>46205</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>46078</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>46251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45792</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46243</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45199</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45694</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45623</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45694</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45694</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45175</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>46126</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>46213</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>46220</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>46220</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45476</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>46266</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46309</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>46251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>46244</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46301</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45892</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>46136</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45751</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45062</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45190</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45709</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45420</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45894</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45213</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46210</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>46220</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44953</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>46282</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>46282</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>46113</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46293</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44942</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>46303</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>46309</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>46265</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>46301</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45834</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45862</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>46099</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44575</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44684</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>44607</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44886</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44862</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44854</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>44550</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44607</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44799</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44854</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44697</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44672</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44616</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44616</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44823</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>44781</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44788</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45146</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44875</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45309</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45077</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45679</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45212</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45454</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45272</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45265</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>45337</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44953</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45665</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44965</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45413</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45237</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45742</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45176</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>45238</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45190</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45219</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45150</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45033</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44832</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45215</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45463</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44726</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45482</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45548</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45469</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45413</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45881</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45463</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45474</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45110</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45887</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45887</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45189</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45888</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45889</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45889</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45579</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45201</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45898</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>46141</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45639</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45834</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46140</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45902</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45902</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45902</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45902</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45561</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45561</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45905</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45839</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45908</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45908</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45121</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45229</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45212</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44505</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45925</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45925</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45665</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45925</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>46149</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45930</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45615</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45936</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45936</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45196</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45943</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45943</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45939</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45892</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44494</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45096</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45148</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45244</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45117</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45552</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45552</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45874</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45894</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45467</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45467</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45946</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45960</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45946</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45705</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45950</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45950</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45960</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45950</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45950</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45952</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45952</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45952</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45150</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45954</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45957</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45955</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45954</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44937</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45960</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45182</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44854</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45972</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45727</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>46162</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45743</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>46163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45980</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>45708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45980</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45980</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>45985</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45986</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44750</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45999</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45999</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45999</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44942</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46169</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45033</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>46003</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46002</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>46008</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44896</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45637</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46008</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45588</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46013</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45573</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46021</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45199</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46029</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44911</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45212</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46175</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46030</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>46030</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46031</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46175</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>46035</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45240</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>46034</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>46034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45688</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>46034</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46038</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>46034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>44953</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46181</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44783</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46057</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46184</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45237</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45615</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46065</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>46065</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>46065</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>46185</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>46185</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46076</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45833</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>46080</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44904</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45463</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>46190</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44942</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45147</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46091</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46091</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46192</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>46191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>46192</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>46100</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46101</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45337</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>46104</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>46195</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46197</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45481</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>46197</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>46114</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>46198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>46197</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46119</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46199</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>46199</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>46122</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45561</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>44609</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>46126</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45154</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44992</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>46127</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45723</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46204</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46133</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46204</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>46134</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46134</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46204</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46204</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46204</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>46205</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>46205</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45027</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45600</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46205</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45264</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46205</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46205</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46206</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45463</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44818</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46210</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46216</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>46216</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>46177</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>44986</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46225</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46225</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46225</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>46225</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46273</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>46273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>46273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>46231</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>46274</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46273</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>46275</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>46275</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45201</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46274</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>46275</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>46231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>46231</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>46274</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>46275</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>45362</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>46279</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>44886</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>46279</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>46279</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>46279</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>46237</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>46274</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>45188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>46281</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>46281</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>46280</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45413</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>46274</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>46273</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>45362</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44953</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>44904</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>46286</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46286</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46244</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>45377</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45870</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45561</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>44550</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45898</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>46243</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>44624</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>46287</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45190</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45237</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45279</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>46248</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45773</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45280</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46293</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>46289</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45112</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>46293</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45908</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>46293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>46293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46204</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45561</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45561</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46286</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>46251</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45051</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46294</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45616</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>46252</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>46252</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44916</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>46296</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>46217</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45727</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>46254</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>46254</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>46254</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>46254</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>46254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46254</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45201</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>46255</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>46300</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>46300</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46301</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>46258</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>46300</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>46300</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>46255</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>46303</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46293</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45792</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45792</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45796</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45797</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45797</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45796</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46120</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45798</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>46266</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>46266</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>46267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>46265</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46309</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46266</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46266</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46267</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>46267</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46309</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45805</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46308</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45805</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>45804</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46265</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45805</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46265</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46266</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>46267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46266</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46267</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>46309</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46266</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45537</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45810</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>46311</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45063</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46269</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45400</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>46269</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46269</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45819</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45414</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>44895</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46310</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45824</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46309</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>46309</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>46267</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45827</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>46311</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>45832</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45833</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45833</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45834</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45834</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45834</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45834</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45840</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45841</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45845</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45843</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45845</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45855</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>45855</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45855</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45870</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>45870</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>45870</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45873</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45798</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45870</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45874</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>45880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45882</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>45882</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>44960</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45027</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44612</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>44943</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45756</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45769</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>46065</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45777</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45777</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>

--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46274</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45945</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>46265</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44739</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45399</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45080</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45744</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45945</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>45744</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44516</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46101</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46314</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>46210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>46274</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>46197</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>46220</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45175</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>46197</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45897</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>46213</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>46197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>46266</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45744</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>46205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45792</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45154</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>46251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45869</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46243</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>46316</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>45012</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45469</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45623</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>46213</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>46220</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>46220</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45476</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>46266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>46309</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>46251</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>46265</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>46244</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>46301</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45694</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45694</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>45175</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45892</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44960</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44953</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45894</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45688</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>46210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>45420</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>46220</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46282</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>46282</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>46113</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>46293</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45213</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45834</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>46092</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>45862</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>46303</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>46265</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>46309</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45751</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>46301</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>46136</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45062</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>44942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45190</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>46099</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44575</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44684</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44607</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44886</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44862</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44550</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44607</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44799</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>44854</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44697</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44672</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>44616</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44616</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>44823</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>44781</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>44788</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45888</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44607</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44624</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>44783</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44942</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45212</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>45889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45033</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44942</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45898</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45561</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45902</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45902</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45902</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45902</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45604</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45908</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45905</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45908</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>46162</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45182</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44832</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44607</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46163</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45190</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45196</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45212</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45925</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45925</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45925</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45930</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45413</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>46175</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>45936</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45413</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45615</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45413</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46175</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45637</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45943</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>44854</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45943</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45467</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>45874</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44494</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45946</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45946</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45096</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45117</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45148</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45552</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45552</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45244</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45874</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45894</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45946</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45467</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45950</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45950</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45950</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>46181</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45950</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45952</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45952</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45952</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45679</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45954</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45954</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45955</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45033</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45957</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45957</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45960</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>46185</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45077</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45121</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>46190</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>46191</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>46192</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45377</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>46192</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45469</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45972</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>46197</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>46197</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>46197</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45463</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45727</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>46199</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>46199</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46198</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46198</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>45980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45980</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45980</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>46204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45215</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>46205</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>46205</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>46204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>46204</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46204</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46205</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>46204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>46206</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>46210</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44904</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45705</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>46216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>46177</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>46216</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45454</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45999</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45999</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45999</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46002</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>46001</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45474</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>46225</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>46225</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>46225</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46225</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46003</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46231</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>46231</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>46008</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46231</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45362</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>46008</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>46279</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>46279</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>46279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>46013</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45362</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46237</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44953</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>46281</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>46021</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>46281</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>46030</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>46280</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46029</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>46030</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>46030</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>46030</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45792</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>46034</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>46286</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>46243</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>46034</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45688</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45240</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>46034</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45463</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>46244</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45870</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45796</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>46035</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45796</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>46038</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>46034</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>46286</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45150</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45798</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45898</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46287</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45797</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45804</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45805</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45908</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45805</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45805</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45810</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46057</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>45537</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>46294</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>46293</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44886</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>46252</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>46293</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>46065</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46065</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>46293</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45400</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>46065</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>46252</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>46293</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>46204</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45063</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45414</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>46248</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45819</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44895</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45824</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>46076</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>46296</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45833</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>46286</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45827</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46251</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45051</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>46254</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>46080</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>46254</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>46254</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>45832</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45834</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>46300</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>46217</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>46254</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>46254</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45834</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45834</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45834</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45833</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46091</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46091</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>46244</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46255</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45840</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46101</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45845</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>45843</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>46300</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45845</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>46100</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46300</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46301</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46255</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>46300</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46258</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45855</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45855</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45855</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>46293</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>46114</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>46303</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46119</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45870</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45870</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45870</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45870</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45874</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>46122</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>46127</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45798</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45873</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>46126</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>46265</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>46308</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45880</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45882</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>46266</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45881</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45882</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>44896</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>46134</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>46134</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>46120</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>46266</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46133</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44992</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45201</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>46265</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46266</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44911</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45280</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46309</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>46309</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46266</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46266</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46310</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46267</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>46309</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>46266</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>46267</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>46267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>46314</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>46314</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>46269</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46314</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>46309</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>46269</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45561</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46311</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>46269</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46309</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45839</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>46314</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>46314</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>46316</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46274</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46274</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>46273</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>46273</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>46140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>46273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>46274</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>46274</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>46315</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>46273</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46273</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>46274</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>46275</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45639</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>46318</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>44953</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>46314</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>46314</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46318</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>46317</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>44960</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>45834</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45212</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45548</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>46141</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46149</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45600</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45960</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45112</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>45463</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>45892</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>45960</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45708</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44750</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45154</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45201</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45150</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>45743</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>45773</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45196</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45742</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45176</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45027</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44965</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45237</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45237</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45238</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45229</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45259</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45588</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45561</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45463</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>44916</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>44550</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45561</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45601</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44937</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45265</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45481</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>44986</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>44818</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45665</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>45573</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>45579</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45196</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45196</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45199</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>44609</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45147</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45146</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45561</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>45561</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>45279</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>44726</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45196</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45201</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45727</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45190</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45309</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>45723</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45264</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45482</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44904</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45219</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45665</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44505</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45337</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45337</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>44875</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>44612</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>44960</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45027</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44943</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45756</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45769</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46065</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45777</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45777</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>

--- a/Översikt GÄLLIVARE.xlsx
+++ b/Översikt GÄLLIVARE.xlsx
@@ -601,7 +601,7 @@
         <v>45832</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45426</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44803</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45832</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45453</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46274</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45945</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>46265</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44739</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45399</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45080</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45744</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45945</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>45744</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45947</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44516</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46101</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46314</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>46274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>46210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>46274</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>46197</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>46220</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45175</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>46197</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45897</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>46213</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>46177</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>46197</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>46266</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45744</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>46205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45792</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45154</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>46251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45869</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46243</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>46316</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>45012</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45469</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45623</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>46213</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>46220</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>46220</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45476</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>46266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>46309</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>46251</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>46265</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>46244</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>46301</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45694</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45694</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>45175</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45892</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44960</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44953</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45894</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45688</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>46210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>45420</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>46220</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46282</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>46282</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>46113</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>46293</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45213</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45834</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>46092</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>45862</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>46303</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>46265</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>46309</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45751</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>46301</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>46136</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45062</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>44942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45190</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>46099</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44575</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44684</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44607</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44886</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44862</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44550</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44607</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44799</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>44854</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44697</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44672</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>44616</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44616</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>44823</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>44781</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>44788</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45888</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44607</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>44624</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>44783</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44942</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45212</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>45889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45033</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>45889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44942</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45898</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45561</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45902</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45902</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45902</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45902</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45604</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45908</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45905</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45908</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>46162</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45182</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44832</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44607</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46163</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45190</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45196</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45212</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45925</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45925</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45925</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45930</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45413</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>46175</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>45936</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45413</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45615</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45413</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46175</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45637</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45943</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>44854</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45943</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45467</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>45874</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44494</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45946</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45946</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45096</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45117</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45148</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45552</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45552</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45244</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45874</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45894</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45946</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45467</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45950</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45950</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45950</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>46181</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45950</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45952</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45952</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45952</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45679</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45954</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45954</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45955</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45033</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45957</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45957</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45960</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>46185</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45077</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45121</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>46190</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>46191</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>46192</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45377</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>46192</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45469</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45972</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>46197</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>46197</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>46197</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45463</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45727</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>46199</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>46199</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46198</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46198</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>45980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45980</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45980</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>46204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45215</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>46205</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>46205</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>46204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>46204</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46204</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46205</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>46204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>46206</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>46210</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44904</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45705</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>46216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>46177</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>46216</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45454</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45999</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45999</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45999</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46002</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>46001</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45474</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>46225</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>46225</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>46225</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46225</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46003</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46231</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>46231</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>46008</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46231</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45362</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>46008</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>46279</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>46279</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>46279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>46013</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45362</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46237</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44953</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>46281</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>46021</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>46281</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>46030</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>46280</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46029</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>46030</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>46030</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>46030</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45792</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>46034</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>46286</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>46031</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>46243</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>46034</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45688</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45240</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>46034</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45463</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>46244</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45870</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45796</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>46035</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45796</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>46038</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>46034</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>46286</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45150</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45798</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45898</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46287</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45797</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45804</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45805</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45908</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45805</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45805</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45810</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46057</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>45537</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>46294</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>46293</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44886</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>46252</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>46293</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>46065</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46065</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>46293</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45400</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>46065</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>46252</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>46293</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>46204</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45063</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45414</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>46248</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45819</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44895</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45824</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>46076</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>46296</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45833</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>46286</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45827</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46251</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45051</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>46254</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>46080</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>46254</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>46254</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>45832</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45834</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>46300</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>46217</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>46254</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>46254</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45834</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45834</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45834</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45833</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46091</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46091</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>46244</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46255</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45840</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46101</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45845</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>45843</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>46300</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45845</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>46100</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46300</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46301</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46255</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>46300</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46258</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45855</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45855</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45855</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>46293</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>46114</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>46303</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46119</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45870</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45870</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45870</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45870</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45874</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>46122</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>46127</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45798</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45873</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>46126</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>46265</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>46308</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45880</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45882</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>46266</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45881</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45882</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>44896</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>46134</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>46134</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>46120</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>46266</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46133</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44992</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45201</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>46265</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46266</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>44911</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45280</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46309</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>46309</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46266</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46266</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46310</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46267</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>46309</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>46266</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>46267</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>46267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>46314</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>46314</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>46269</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46314</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>46309</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>46269</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45561</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46311</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>46269</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46309</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45839</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>46314</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>46314</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>46316</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46274</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46274</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>46273</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>46273</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>46140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>46273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>46274</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>46274</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>46315</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>46273</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46273</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>46274</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>46275</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45639</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>46318</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>44953</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>46314</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>46314</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46318</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>46317</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>44960</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>45834</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45212</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45548</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>46141</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46149</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45600</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45960</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45112</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>45463</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>45892</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>45960</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45708</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44750</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45154</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45201</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45150</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>45743</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>45773</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45196</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45742</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45176</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45027</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44965</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45237</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45237</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45238</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45229</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45259</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45588</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45561</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45463</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>44916</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>44550</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45561</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45601</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44937</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45265</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45481</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>44986</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>44818</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45665</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>45573</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>45579</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45196</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45196</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45199</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>44609</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45147</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45146</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45561</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>45561</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>45279</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>44726</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45196</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45201</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45727</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45190</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45309</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>45723</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45264</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45482</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44904</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45219</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45665</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>44505</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45337</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45337</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>44875</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>44612</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>44960</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45027</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44943</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45756</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45769</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46065</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45777</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45777</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
